--- a/resources/M678/spc_sheet_oos_detail.xlsx
+++ b/resources/M678/spc_sheet_oos_detail.xlsx
@@ -1126,7 +1126,7 @@
         <v>-3.0885</v>
       </c>
       <c r="I8">
-        <v>0.0131078947368421</v>
+        <v>0.01310789473684211</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -2114,7 +2114,7 @@
         <v>-7.2604</v>
       </c>
       <c r="I34">
-        <v>-1.400568421052632</v>
+        <v>-1.400568421052631</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -2418,7 +2418,7 @@
         <v>-5.4398</v>
       </c>
       <c r="I42">
-        <v>-0.508538596491228</v>
+        <v>-0.5085385964912281</v>
       </c>
       <c r="J42">
         <v>6</v>
@@ -2456,7 +2456,7 @@
         <v>-5.7136</v>
       </c>
       <c r="I43">
-        <v>0.175659649122807</v>
+        <v>0.1756596491228071</v>
       </c>
       <c r="J43">
         <v>6</v>
@@ -2912,7 +2912,7 @@
         <v>-5.1932</v>
       </c>
       <c r="I55">
-        <v>0.04012719298245613</v>
+        <v>0.04012719298245614</v>
       </c>
       <c r="J55">
         <v>6</v>
@@ -3102,7 +3102,7 @@
         <v>-5.6846</v>
       </c>
       <c r="I60">
-        <v>-0.06024385964912281</v>
+        <v>-0.0602438596491228</v>
       </c>
       <c r="J60">
         <v>6</v>
@@ -3672,7 +3672,7 @@
         <v>-4.3387</v>
       </c>
       <c r="I75">
-        <v>0.07310614035087719</v>
+        <v>0.0731061403508772</v>
       </c>
       <c r="J75">
         <v>6</v>
@@ -3748,7 +3748,7 @@
         <v>-2.9467</v>
       </c>
       <c r="I77">
-        <v>0.8123438596491227</v>
+        <v>0.8123438596491228</v>
       </c>
       <c r="J77">
         <v>6</v>
@@ -4166,7 +4166,7 @@
         <v>-3.4868</v>
       </c>
       <c r="I88">
-        <v>0.7402166666666667</v>
+        <v>0.7402166666666666</v>
       </c>
       <c r="J88">
         <v>6</v>
@@ -4660,7 +4660,7 @@
         <v>-3.7796</v>
       </c>
       <c r="I101">
-        <v>0.04655438596491229</v>
+        <v>0.04655438596491231</v>
       </c>
       <c r="J101">
         <v>6</v>
@@ -4812,7 +4812,7 @@
         <v>-6.0523</v>
       </c>
       <c r="I105">
-        <v>-0.2121008771929824</v>
+        <v>-0.2121008771929825</v>
       </c>
       <c r="J105">
         <v>6</v>
@@ -5002,7 +5002,7 @@
         <v>-5.8161</v>
       </c>
       <c r="I110">
-        <v>2.603806140350877</v>
+        <v>2.603806140350878</v>
       </c>
       <c r="J110">
         <v>6</v>
@@ -5040,7 +5040,7 @@
         <v>-8.9049</v>
       </c>
       <c r="I111">
-        <v>0.07020701754385966</v>
+        <v>0.07020701754385963</v>
       </c>
       <c r="J111">
         <v>6</v>
@@ -5458,7 +5458,7 @@
         <v>-6.0937</v>
       </c>
       <c r="I122">
-        <v>0.7741403508771929</v>
+        <v>0.774140350877193</v>
       </c>
       <c r="J122">
         <v>6</v>
@@ -6066,7 +6066,7 @@
         <v>-5.6842</v>
       </c>
       <c r="I138">
-        <v>-0.4003035087719298</v>
+        <v>-0.4003035087719299</v>
       </c>
       <c r="J138">
         <v>6</v>
@@ -6218,7 +6218,7 @@
         <v>-6.1442</v>
       </c>
       <c r="I142">
-        <v>-0.8545333333333333</v>
+        <v>-0.8545333333333334</v>
       </c>
       <c r="J142">
         <v>6</v>
@@ -6712,7 +6712,7 @@
         <v>-3.7281</v>
       </c>
       <c r="I155">
-        <v>0.7234912280701754</v>
+        <v>0.7234912280701755</v>
       </c>
       <c r="J155">
         <v>6</v>
@@ -7624,7 +7624,7 @@
         <v>-7.4452</v>
       </c>
       <c r="I179">
-        <v>-0.6949333333333333</v>
+        <v>-0.6949333333333334</v>
       </c>
       <c r="J179">
         <v>6</v>
@@ -7852,7 +7852,7 @@
         <v>-5.6525</v>
       </c>
       <c r="I185">
-        <v>-0.05103859649122806</v>
+        <v>-0.05103859649122805</v>
       </c>
       <c r="J185">
         <v>6</v>
@@ -8536,7 +8536,7 @@
         <v>-6.2446</v>
       </c>
       <c r="I203">
-        <v>0.02668684210526316</v>
+        <v>0.02668684210526317</v>
       </c>
       <c r="J203">
         <v>6</v>
@@ -8650,7 +8650,7 @@
         <v>-6.4126</v>
       </c>
       <c r="I206">
-        <v>-0.184828947368421</v>
+        <v>-0.1848289473684211</v>
       </c>
       <c r="J206">
         <v>6</v>
@@ -8764,7 +8764,7 @@
         <v>-6.4055</v>
       </c>
       <c r="I209">
-        <v>0.4744570175438596</v>
+        <v>0.4744570175438597</v>
       </c>
       <c r="J209">
         <v>6</v>
@@ -8802,7 +8802,7 @@
         <v>-4.6724</v>
       </c>
       <c r="I210">
-        <v>-0.1550692982456141</v>
+        <v>-0.155069298245614</v>
       </c>
       <c r="J210">
         <v>6</v>
@@ -9220,7 +9220,7 @@
         <v>-6.0526</v>
       </c>
       <c r="I221">
-        <v>-2.096081578947369</v>
+        <v>-2.096081578947368</v>
       </c>
       <c r="J221">
         <v>6</v>
@@ -10930,7 +10930,7 @@
         <v>-3.3894</v>
       </c>
       <c r="I266">
-        <v>1.188629824561403</v>
+        <v>1.188629824561404</v>
       </c>
       <c r="J266">
         <v>6</v>
@@ -11120,7 +11120,7 @@
         <v>-7.4914</v>
       </c>
       <c r="I271">
-        <v>0.1023745614035088</v>
+        <v>0.1023745614035087</v>
       </c>
       <c r="J271">
         <v>6</v>

--- a/resources/M678/spc_sheet_oos_detail.xlsx
+++ b/resources/M678/spc_sheet_oos_detail.xlsx
@@ -1126,7 +1126,7 @@
         <v>-3.0885</v>
       </c>
       <c r="I8">
-        <v>0.01310789473684211</v>
+        <v>0.01310789473684213</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1430,7 +1430,7 @@
         <v>-4.8336</v>
       </c>
       <c r="I16">
-        <v>-0.3281973684210527</v>
+        <v>-0.3281973684210526</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -1468,7 +1468,7 @@
         <v>-6.6533</v>
       </c>
       <c r="I17">
-        <v>-0.9426131578947368</v>
+        <v>-0.9426131578947369</v>
       </c>
       <c r="J17">
         <v>6</v>
@@ -2114,7 +2114,7 @@
         <v>-7.2604</v>
       </c>
       <c r="I34">
-        <v>-1.400568421052631</v>
+        <v>-1.400568421052632</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -2342,7 +2342,7 @@
         <v>-6.0781</v>
       </c>
       <c r="I40">
-        <v>-0.6418736842105263</v>
+        <v>-0.6418736842105264</v>
       </c>
       <c r="J40">
         <v>6</v>
@@ -2456,7 +2456,7 @@
         <v>-5.7136</v>
       </c>
       <c r="I43">
-        <v>0.1756596491228071</v>
+        <v>0.175659649122807</v>
       </c>
       <c r="J43">
         <v>6</v>
@@ -2836,7 +2836,7 @@
         <v>-6.233</v>
       </c>
       <c r="I53">
-        <v>-0.5874508771929825</v>
+        <v>-0.5874508771929824</v>
       </c>
       <c r="J53">
         <v>6</v>
@@ -3102,7 +3102,7 @@
         <v>-5.6846</v>
       </c>
       <c r="I60">
-        <v>-0.0602438596491228</v>
+        <v>-0.06024385964912281</v>
       </c>
       <c r="J60">
         <v>6</v>
@@ -3672,7 +3672,7 @@
         <v>-4.3387</v>
       </c>
       <c r="I75">
-        <v>0.0731061403508772</v>
+        <v>0.07310614035087719</v>
       </c>
       <c r="J75">
         <v>6</v>
@@ -3710,7 +3710,7 @@
         <v>-4.2277</v>
       </c>
       <c r="I76">
-        <v>0.04920350877192983</v>
+        <v>0.04920350877192985</v>
       </c>
       <c r="J76">
         <v>6</v>
@@ -4166,7 +4166,7 @@
         <v>-3.4868</v>
       </c>
       <c r="I88">
-        <v>0.7402166666666666</v>
+        <v>0.7402166666666667</v>
       </c>
       <c r="J88">
         <v>6</v>
@@ -4470,7 +4470,7 @@
         <v>-5.1219</v>
       </c>
       <c r="I96">
-        <v>0.03223245614035086</v>
+        <v>0.03223245614035085</v>
       </c>
       <c r="J96">
         <v>6</v>
@@ -4660,7 +4660,7 @@
         <v>-3.7796</v>
       </c>
       <c r="I101">
-        <v>0.04655438596491231</v>
+        <v>0.04655438596491228</v>
       </c>
       <c r="J101">
         <v>6</v>
@@ -4736,7 +4736,7 @@
         <v>-5.6246</v>
       </c>
       <c r="I103">
-        <v>-0.673040350877193</v>
+        <v>-0.6730403508771929</v>
       </c>
       <c r="J103">
         <v>6</v>
@@ -4888,7 +4888,7 @@
         <v>-5.4294</v>
       </c>
       <c r="I107">
-        <v>-0.01897456140350878</v>
+        <v>-0.01897456140350881</v>
       </c>
       <c r="J107">
         <v>6</v>
@@ -5306,7 +5306,7 @@
         <v>-5.9926</v>
       </c>
       <c r="I118">
-        <v>-0.8746192982456141</v>
+        <v>-0.874619298245614</v>
       </c>
       <c r="J118">
         <v>6</v>
@@ -5458,7 +5458,7 @@
         <v>-6.0937</v>
       </c>
       <c r="I122">
-        <v>0.774140350877193</v>
+        <v>0.7741403508771929</v>
       </c>
       <c r="J122">
         <v>6</v>
@@ -5496,7 +5496,7 @@
         <v>-6.3101</v>
       </c>
       <c r="I123">
-        <v>0.08464298245614034</v>
+        <v>0.08464298245614035</v>
       </c>
       <c r="J123">
         <v>6</v>
@@ -5686,7 +5686,7 @@
         <v>-4.412</v>
       </c>
       <c r="I128">
-        <v>-0.06693508771929822</v>
+        <v>-0.06693508771929824</v>
       </c>
       <c r="J128">
         <v>6</v>
@@ -5838,7 +5838,7 @@
         <v>-8.2218</v>
       </c>
       <c r="I132">
-        <v>0.08150438596491225</v>
+        <v>0.0815043859649123</v>
       </c>
       <c r="J132">
         <v>6</v>
@@ -6066,7 +6066,7 @@
         <v>-5.6842</v>
       </c>
       <c r="I138">
-        <v>-0.4003035087719299</v>
+        <v>-0.4003035087719298</v>
       </c>
       <c r="J138">
         <v>6</v>
@@ -6218,7 +6218,7 @@
         <v>-6.1442</v>
       </c>
       <c r="I142">
-        <v>-0.8545333333333334</v>
+        <v>-0.8545333333333333</v>
       </c>
       <c r="J142">
         <v>6</v>
@@ -7016,7 +7016,7 @@
         <v>-6.3979</v>
       </c>
       <c r="I163">
-        <v>-1.575316666666666</v>
+        <v>-1.575316666666667</v>
       </c>
       <c r="J163">
         <v>6</v>
@@ -7624,7 +7624,7 @@
         <v>-7.4452</v>
       </c>
       <c r="I179">
-        <v>-0.6949333333333334</v>
+        <v>-0.6949333333333333</v>
       </c>
       <c r="J179">
         <v>6</v>
@@ -7852,7 +7852,7 @@
         <v>-5.6525</v>
       </c>
       <c r="I185">
-        <v>-0.05103859649122805</v>
+        <v>-0.05103859649122806</v>
       </c>
       <c r="J185">
         <v>6</v>
@@ -8346,7 +8346,7 @@
         <v>-4.158</v>
       </c>
       <c r="I198">
-        <v>0.6057271929824561</v>
+        <v>0.6057271929824563</v>
       </c>
       <c r="J198">
         <v>6</v>
@@ -8536,7 +8536,7 @@
         <v>-6.2446</v>
       </c>
       <c r="I203">
-        <v>0.02668684210526317</v>
+        <v>0.02668684210526315</v>
       </c>
       <c r="J203">
         <v>6</v>
@@ -8764,7 +8764,7 @@
         <v>-6.4055</v>
       </c>
       <c r="I209">
-        <v>0.4744570175438597</v>
+        <v>0.4744570175438596</v>
       </c>
       <c r="J209">
         <v>6</v>
@@ -8802,7 +8802,7 @@
         <v>-4.6724</v>
       </c>
       <c r="I210">
-        <v>-0.155069298245614</v>
+        <v>-0.1550692982456141</v>
       </c>
       <c r="J210">
         <v>6</v>
@@ -10930,7 +10930,7 @@
         <v>-3.3894</v>
       </c>
       <c r="I266">
-        <v>1.188629824561404</v>
+        <v>1.188629824561403</v>
       </c>
       <c r="J266">
         <v>6</v>
@@ -10968,7 +10968,7 @@
         <v>-3.9145</v>
       </c>
       <c r="I267">
-        <v>0.08487368421052632</v>
+        <v>0.08487368421052631</v>
       </c>
       <c r="J267">
         <v>6</v>
@@ -11120,7 +11120,7 @@
         <v>-7.4914</v>
       </c>
       <c r="I271">
-        <v>0.1023745614035087</v>
+        <v>0.1023745614035088</v>
       </c>
       <c r="J271">
         <v>6</v>
